--- a/12615394.xlsx
+++ b/12615394.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -189,9 +189,6 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
-  </si>
-  <si>
     <t>5. GOOD PRACTICE</t>
   </si>
   <si>
@@ -207,31 +204,10 @@
     <t>high</t>
   </si>
   <si>
-    <t>Relaxed</t>
-  </si>
-  <si>
     <t>completed my work early and spent some time doing things I enjoy.</t>
   </si>
   <si>
-    <t>tired</t>
-  </si>
-  <si>
-    <t>satisfied</t>
-  </si>
-  <si>
-    <t>low</t>
-  </si>
-  <si>
     <t>classes were long today. Couldn't concentrate much after coming home.</t>
-  </si>
-  <si>
-    <t>relaxed</t>
-  </si>
-  <si>
-    <t>very satisfied</t>
-  </si>
-  <si>
-    <t>medium</t>
   </si>
   <si>
     <t>took some rest and prepared for the coming week.</t>
@@ -240,31 +216,13 @@
     <t>long day . Exhausted.</t>
   </si>
   <si>
-    <t>satsfied</t>
-  </si>
-  <si>
-    <t>mediium</t>
-  </si>
-  <si>
-    <t>neutral</t>
-  </si>
-  <si>
     <t>I attend  8 long classes and spend 3-4 hours travelling . After coming home I feel completely exhausted.</t>
-  </si>
-  <si>
-    <t>good</t>
   </si>
   <si>
     <t>today, I have only 5 classes so I reach home early and have enough time to focus on my studies.</t>
   </si>
   <si>
-    <t>very good</t>
-  </si>
-  <si>
     <t>I have only 3 classes today so I reach home early . After taking some rest . I start preparing for my tomorrow's DBMS CA.</t>
-  </si>
-  <si>
-    <t>satisied</t>
   </si>
   <si>
     <t>today is my DBMS CA and it goes very well. It is quite easy and after completing it I feel very happy.</t>
@@ -279,9 +237,6 @@
     <t>today is Sunday, so I focus on my studies and prepare for the upcoming week.</t>
   </si>
   <si>
-    <t>exhausted</t>
-  </si>
-  <si>
     <t>its Monday. Very long day just exhausted.</t>
   </si>
   <si>
@@ -291,10 +246,100 @@
     <t>8 classes- long day - tired.</t>
   </si>
   <si>
-    <t>enjoy Sunday</t>
+    <t>after long and tiring week ,I take some much needed rest and focus more on my studies. I feel relaxed and prepare myself for upcoming exams.</t>
   </si>
   <si>
-    <t>after long and tiring week ,I take some much needed rest and focus more on my studies. I feel relaxed and prepare myself for upcoming exams.</t>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>I reach home early because my classes finish at 2:30 pm. I get more time to focus on my studies and use the extra time poductively.</t>
+  </si>
+  <si>
+    <t>overall , it’s a good day . I spend more time with my family and enjoy their company.</t>
+  </si>
+  <si>
+    <t>I feel happy , ralaxed and satisfied with how I spend my day.</t>
+  </si>
+  <si>
+    <t>I feel exhausted after attending long classes. At the same time, I feel happy because the weekend has finally arrived.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Finaaly weekend has arrived , now I can take some rest , relax and enjoy my weekend.</t>
+  </si>
+  <si>
+    <t>overall , it's a good day.</t>
+  </si>
+  <si>
+    <t>Reach home early and spend time playing with my nephew. We have a really good time together, which makes me feel happy and relaxed.</t>
+  </si>
+  <si>
+    <t>toady is Saturday, so after a long and tiring week, I finally get some time to slow down and relax.</t>
+  </si>
+  <si>
+    <t>Today,my nephew completes eight months, so my family and I celebrate this little milestone together.</t>
+  </si>
+  <si>
+    <t>I reach home early and some quality time with my friend.</t>
+  </si>
+  <si>
+    <t>My calsses start at 11:10, so I wake up little late and get some extra sleep</t>
+  </si>
+  <si>
+    <t>I have a good day and spend some time preparing for my upcoming CA.</t>
+  </si>
+  <si>
+    <t>After attending 8 classes , I feel really low and exhausted. When I reach home , I have my dinner and go straight to bed.</t>
+  </si>
+  <si>
+    <t>Normal day with my usual routine. I attended 5 classes and follow my regular schedule.</t>
+  </si>
+  <si>
+    <t>I am very happy because I only have 3 classes to attend . This gives me plenty of time to relax and focus on other things.</t>
+  </si>
+  <si>
+    <t>I have a relaxed and enjoyable day.</t>
+  </si>
+  <si>
+    <t>Its Sunday , so I have plenty of time to focus on my studies and take care of other things.</t>
+  </si>
+  <si>
+    <t>Today , I have some important work to take care of, so I attend only 2  classes.</t>
+  </si>
+  <si>
+    <t>Today is Wednesday , ihave only 3 classes so I'm very happly.</t>
+  </si>
+  <si>
+    <t>I get enough time to rest and focus on my studies. I feel relaxed and use my time well to stay productive.</t>
+  </si>
+  <si>
+    <t>Normal day with my usual routine. Manage my time well, and get enough time for my daily activities.</t>
+  </si>
+  <si>
+    <t>I'm feeling little tired but also happy because tomorrow  is Saturday.</t>
+  </si>
+  <si>
+    <t>I feel  a little tired this morning and find it hard to get up after a long and tiring Monday  with so many classes. Still, I enjoy my day and try to make the most of it.</t>
+  </si>
+  <si>
+    <t>Today is a good day. After reaching home I spend some quality time with my nephew.</t>
+  </si>
+  <si>
+    <t>I simply relaxand enjoy my day with my family.</t>
   </si>
 </sst>
 </file>
@@ -911,7 +956,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -981,7 +1026,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -998,7 +1043,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1006,7 +1051,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1072,7 +1117,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="57" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>46247</v>
       </c>
@@ -1115,7 +1160,7 @@
         <v>51</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -1152,16 +1197,16 @@
         <v>280</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -1198,16 +1243,16 @@
         <v>340</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="L8" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N8" s="17" t="s">
         <v>57</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -1244,16 +1289,16 @@
         <v>360</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1293,16 +1338,16 @@
         <v>73</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>46252</v>
       </c>
@@ -1336,15 +1381,17 @@
         <v>220</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N11" s="17"/>
+        <v>77</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
@@ -1380,17 +1427,19 @@
         <v>230</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <v>46254</v>
       </c>
@@ -1424,17 +1473,19 @@
         <v>180</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N13" s="17"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>46255</v>
       </c>
@@ -1468,17 +1519,19 @@
         <v>110</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="N14" s="17"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>46256</v>
       </c>
@@ -1512,17 +1565,19 @@
         <v>570</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <v>46257</v>
       </c>
@@ -1556,17 +1611,19 @@
         <v>495</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
         <v>46258</v>
       </c>
@@ -1600,17 +1657,19 @@
         <v>190</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <v>46259</v>
       </c>
@@ -1650,11 +1709,13 @@
         <v>50</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
         <v>46260</v>
       </c>
@@ -1688,17 +1749,19 @@
         <v>130</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <v>46261</v>
       </c>
@@ -1738,11 +1801,13 @@
         <v>50</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <v>46262</v>
       </c>
@@ -1779,14 +1844,16 @@
         <v>49</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M21" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N21" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
         <v>46263</v>
       </c>
@@ -1820,17 +1887,19 @@
         <v>560</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
         <v>46264</v>
       </c>
@@ -1864,17 +1933,19 @@
         <v>480</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
         <v>46265</v>
       </c>
@@ -1908,17 +1979,19 @@
         <v>320</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="105" x14ac:dyDescent="0.25">
       <c r="A25" s="13">
         <v>46266</v>
       </c>
@@ -1952,17 +2025,19 @@
         <v>195</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L25" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
         <v>46267</v>
       </c>
@@ -1996,17 +2071,19 @@
         <v>110</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
         <v>46268</v>
       </c>
@@ -2046,11 +2123,13 @@
         <v>50</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="13">
         <v>46269</v>
       </c>
@@ -2090,11 +2169,13 @@
         <v>50</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="13">
         <v>46270</v>
       </c>
@@ -2128,17 +2209,19 @@
         <v>600</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
         <v>46271</v>
       </c>
@@ -2172,15 +2255,17 @@
         <v>575</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
@@ -2216,16 +2301,16 @@
         <v>180</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N31" s="17" t="s">
         <v>61</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N31" s="17" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -2262,16 +2347,16 @@
         <v>270</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="75" x14ac:dyDescent="0.25">
@@ -2308,16 +2393,16 @@
         <v>185</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -2354,16 +2439,16 @@
         <v>280</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="M34" s="16" t="s">
-        <v>57</v>
-      </c>
       <c r="N34" s="17" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="90" x14ac:dyDescent="0.25">
@@ -2400,19 +2485,19 @@
         <v>350</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="13">
         <v>46277</v>
       </c>
@@ -2446,16 +2531,16 @@
         <v>600</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -2492,16 +2577,16 @@
         <v>510</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -2538,19 +2623,19 @@
         <v>200</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
         <v>46280</v>
       </c>
@@ -2584,17 +2669,19 @@
         <v>230</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="13">
         <v>46281</v>
       </c>
@@ -2628,17 +2715,19 @@
         <v>260</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="13">
         <v>46282</v>
       </c>
@@ -2672,15 +2761,17 @@
         <v>300</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N41" s="17"/>
+        <v>77</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="42" spans="1:14" ht="105" x14ac:dyDescent="0.25">
       <c r="A42" s="13">
@@ -2716,16 +2807,16 @@
         <v>450</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="90" x14ac:dyDescent="0.25">
@@ -2762,19 +2853,19 @@
         <v>450</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="13">
         <v>46285</v>
       </c>
@@ -2808,16 +2899,16 @@
         <v>400</v>
       </c>
       <c r="K44" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L44" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M44" s="16" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -2854,16 +2945,16 @@
         <v>160</v>
       </c>
       <c r="K45" s="16" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L45" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M45" s="16" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="N45" s="17" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">

--- a/12615394.xlsx
+++ b/12615394.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -199,9 +199,6 @@
   </si>
   <si>
     <t>August to September</t>
-  </si>
-  <si>
-    <t>high</t>
   </si>
   <si>
     <t>completed my work early and spent some time doing things I enjoy.</t>
@@ -989,7 +986,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N400"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1143,11 +1140,11 @@
         <v>300</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I68" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1165</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J68" si="1">IF(I6="","",1440-I6)</f>
         <v>275</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1160,7 +1157,7 @@
         <v>51</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -1197,16 +1194,16 @@
         <v>280</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -1243,16 +1240,16 @@
         <v>340</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L8" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -1289,16 +1286,16 @@
         <v>360</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M9" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1335,16 +1332,16 @@
         <v>180</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L10" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="75" x14ac:dyDescent="0.25">
@@ -1381,16 +1378,16 @@
         <v>220</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M11" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1427,16 +1424,16 @@
         <v>230</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L12" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M12" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="M12" s="16" t="s">
-        <v>77</v>
-      </c>
       <c r="N12" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="90" x14ac:dyDescent="0.25">
@@ -1479,10 +1476,10 @@
         <v>50</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="75" x14ac:dyDescent="0.25">
@@ -1528,7 +1525,7 @@
         <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -1565,7 +1562,7 @@
         <v>570</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L15" s="16" t="s">
         <v>50</v>
@@ -1574,7 +1571,7 @@
         <v>51</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -1611,7 +1608,7 @@
         <v>495</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L16" s="16" t="s">
         <v>50</v>
@@ -1620,7 +1617,7 @@
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="75" x14ac:dyDescent="0.25">
@@ -1657,16 +1654,16 @@
         <v>190</v>
       </c>
       <c r="K17" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M17" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="L17" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>75</v>
-      </c>
       <c r="N17" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -1709,10 +1706,10 @@
         <v>50</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="75" x14ac:dyDescent="0.25">
@@ -1749,16 +1746,16 @@
         <v>130</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L19" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M19" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="M19" s="16" t="s">
-        <v>77</v>
-      </c>
       <c r="N19" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -1801,10 +1798,10 @@
         <v>50</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -1850,7 +1847,7 @@
         <v>51</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -1887,16 +1884,16 @@
         <v>560</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L22" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -1933,7 +1930,7 @@
         <v>480</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L23" s="16" t="s">
         <v>50</v>
@@ -1942,7 +1939,7 @@
         <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -1985,10 +1982,10 @@
         <v>50</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="105" x14ac:dyDescent="0.25">
@@ -2025,16 +2022,16 @@
         <v>195</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L25" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -2071,16 +2068,16 @@
         <v>110</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L26" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M26" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="M26" s="16" t="s">
-        <v>77</v>
-      </c>
       <c r="N26" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -2123,10 +2120,10 @@
         <v>50</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -2169,10 +2166,10 @@
         <v>50</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -2209,7 +2206,7 @@
         <v>600</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L29" s="16" t="s">
         <v>50</v>
@@ -2218,7 +2215,7 @@
         <v>51</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="75" x14ac:dyDescent="0.25">
@@ -2255,7 +2252,7 @@
         <v>575</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L30" s="16" t="s">
         <v>50</v>
@@ -2264,7 +2261,7 @@
         <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -2301,16 +2298,16 @@
         <v>180</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L31" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -2350,13 +2347,13 @@
         <v>49</v>
       </c>
       <c r="L32" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M32" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="M32" s="16" t="s">
-        <v>77</v>
-      </c>
       <c r="N32" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="75" x14ac:dyDescent="0.25">
@@ -2393,16 +2390,16 @@
         <v>185</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L33" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M33" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="M33" s="16" t="s">
-        <v>77</v>
-      </c>
       <c r="N33" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -2445,10 +2442,10 @@
         <v>50</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="90" x14ac:dyDescent="0.25">
@@ -2485,16 +2482,16 @@
         <v>350</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L35" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="60" x14ac:dyDescent="0.25">
@@ -2531,7 +2528,7 @@
         <v>600</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L36" s="16" t="s">
         <v>50</v>
@@ -2540,7 +2537,7 @@
         <v>51</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -2577,7 +2574,7 @@
         <v>510</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L37" s="16" t="s">
         <v>50</v>
@@ -2586,7 +2583,7 @@
         <v>51</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -2623,16 +2620,16 @@
         <v>200</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L38" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -2675,10 +2672,10 @@
         <v>50</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -2715,16 +2712,16 @@
         <v>260</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L40" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -2767,10 +2764,10 @@
         <v>50</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="105" x14ac:dyDescent="0.25">
@@ -2816,7 +2813,7 @@
         <v>51</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="90" x14ac:dyDescent="0.25">
@@ -2853,16 +2850,16 @@
         <v>450</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L43" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -2899,7 +2896,7 @@
         <v>400</v>
       </c>
       <c r="K44" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L44" s="16" t="s">
         <v>50</v>
@@ -2908,7 +2905,7 @@
         <v>51</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -2945,16 +2942,16 @@
         <v>160</v>
       </c>
       <c r="K45" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L45" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M45" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N45" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -3143,11 +3140,11 @@
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
       <c r="I54" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I54:I55" si="2">IF(SUM(B54:F54,H54)=0,"",SUM(B54:F54,H54))</f>
         <v/>
       </c>
       <c r="J54" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J54:J55" si="3">IF(I54="","",1440-I54)</f>
         <v/>
       </c>
       <c r="K54" s="16"/>
@@ -3165,11 +3162,11 @@
       <c r="G55" s="14"/>
       <c r="H55" s="14"/>
       <c r="I55" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J55" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K55" s="16"/>
@@ -3473,11 +3470,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I69:I132" si="4">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J69:J132" si="5">IF(I69="","",1440-I69)</f>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3495,11 +3492,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3517,11 +3514,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3539,11 +3536,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3561,11 +3558,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3583,11 +3580,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3605,11 +3602,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3627,11 +3624,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3649,11 +3646,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3671,11 +3668,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3693,11 +3690,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3715,11 +3712,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3737,11 +3734,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3759,11 +3756,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3781,11 +3778,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3803,11 +3800,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3825,11 +3822,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3847,11 +3844,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3869,11 +3866,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3891,11 +3888,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3913,11 +3910,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3935,11 +3932,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3957,11 +3954,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3979,11 +3976,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -4001,11 +3998,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -4023,11 +4020,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -4045,11 +4042,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -4067,11 +4064,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -4089,11 +4086,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -4111,11 +4108,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -4133,11 +4130,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -4155,11 +4152,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -4177,11 +4174,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -4199,11 +4196,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4221,11 +4218,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4243,11 +4240,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4265,11 +4262,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4287,11 +4284,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4309,11 +4306,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4331,11 +4328,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4353,11 +4350,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4375,11 +4372,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4397,11 +4394,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4419,11 +4416,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4441,11 +4438,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4463,11 +4460,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4485,11 +4482,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4507,11 +4504,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4529,11 +4526,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4551,11 +4548,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4573,11 +4570,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4595,11 +4592,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4617,11 +4614,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4639,11 +4636,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4661,11 +4658,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4683,11 +4680,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4705,11 +4702,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4727,11 +4724,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4749,11 +4746,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4771,11 +4768,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4793,11 +4790,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4815,11 +4812,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4837,11 +4834,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4859,11 +4856,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4881,11 +4878,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I133:I196" si="6">IF(SUM(B133:F133,H133)=0,"",SUM(B133:F133,H133))</f>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J133:J196" si="7">IF(I133="","",1440-I133)</f>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4903,11 +4900,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4925,11 +4922,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4947,11 +4944,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4969,11 +4966,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4991,11 +4988,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -5013,11 +5010,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -5035,11 +5032,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5057,11 +5054,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5079,11 +5076,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -5101,11 +5098,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -5123,11 +5120,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -5145,11 +5142,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -5167,11 +5164,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -5189,11 +5186,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5211,11 +5208,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5233,11 +5230,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5255,11 +5252,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5277,11 +5274,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5299,11 +5296,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5321,11 +5318,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5343,11 +5340,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5365,11 +5362,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5387,11 +5384,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5409,11 +5406,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5431,11 +5428,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5453,11 +5450,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5475,11 +5472,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5497,11 +5494,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5519,11 +5516,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5541,11 +5538,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5563,11 +5560,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5585,11 +5582,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5607,11 +5604,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5629,11 +5626,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5651,11 +5648,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5673,11 +5670,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5695,11 +5692,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5717,11 +5714,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5739,11 +5736,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5761,11 +5758,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5783,11 +5780,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5805,11 +5802,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5827,11 +5824,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5849,11 +5846,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5871,11 +5868,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5893,11 +5890,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5915,11 +5912,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5937,11 +5934,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5959,11 +5956,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5981,11 +5978,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -6003,11 +6000,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -6025,11 +6022,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6047,11 +6044,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6069,11 +6066,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6091,11 +6088,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -6113,11 +6110,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6135,11 +6132,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6157,11 +6154,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6179,11 +6176,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6201,11 +6198,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6223,11 +6220,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6245,11 +6242,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6267,11 +6264,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6289,11 +6286,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I197:I260" si="8">IF(SUM(B197:F197,H197)=0,"",SUM(B197:F197,H197))</f>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J197:J260" si="9">IF(I197="","",1440-I197)</f>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6311,11 +6308,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6333,11 +6330,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6355,11 +6352,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6377,11 +6374,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6399,11 +6396,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6421,11 +6418,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6443,11 +6440,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6465,11 +6462,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6487,11 +6484,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6509,11 +6506,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6531,11 +6528,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6553,11 +6550,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6575,11 +6572,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6597,11 +6594,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6619,11 +6616,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6641,11 +6638,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6663,11 +6660,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6685,11 +6682,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6707,11 +6704,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6729,11 +6726,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6751,11 +6748,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6773,11 +6770,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6795,11 +6792,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6817,11 +6814,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6839,11 +6836,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6861,11 +6858,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6883,11 +6880,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6905,11 +6902,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6927,11 +6924,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6949,11 +6946,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6971,11 +6968,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6993,11 +6990,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -7015,11 +7012,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -7037,11 +7034,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7059,11 +7056,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7081,11 +7078,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7103,11 +7100,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -7125,11 +7122,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -7147,11 +7144,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -7169,11 +7166,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -7191,11 +7188,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7213,11 +7210,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7235,11 +7232,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7257,11 +7254,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7279,11 +7276,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7301,11 +7298,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7323,11 +7320,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7345,11 +7342,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7367,11 +7364,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7389,11 +7386,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7411,11 +7408,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7433,11 +7430,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7455,11 +7452,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7477,11 +7474,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7499,11 +7496,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7521,11 +7518,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7543,11 +7540,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7565,11 +7562,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7587,11 +7584,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7609,11 +7606,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7631,11 +7628,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7653,11 +7650,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7675,11 +7672,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7697,11 +7694,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I261:I324" si="10">IF(SUM(B261:F261,H261)=0,"",SUM(B261:F261,H261))</f>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J261:J324" si="11">IF(I261="","",1440-I261)</f>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7719,11 +7716,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7741,11 +7738,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7763,11 +7760,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7785,11 +7782,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7807,11 +7804,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7829,11 +7826,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7851,11 +7848,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7873,11 +7870,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7895,11 +7892,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7917,11 +7914,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7939,11 +7936,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7961,11 +7958,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7983,11 +7980,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -8005,11 +8002,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -8027,11 +8024,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8049,11 +8046,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8071,11 +8068,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8093,11 +8090,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -8115,11 +8112,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -8137,11 +8134,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -8159,11 +8156,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -8181,11 +8178,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -8203,11 +8200,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8225,11 +8222,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8247,11 +8244,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8269,11 +8266,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8291,11 +8288,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8313,11 +8310,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8335,11 +8332,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8357,11 +8354,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8379,11 +8376,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8401,11 +8398,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8423,11 +8420,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8445,11 +8442,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8467,11 +8464,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8489,11 +8486,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8511,11 +8508,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8533,11 +8530,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8555,11 +8552,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8577,11 +8574,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8599,11 +8596,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8621,11 +8618,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8643,11 +8640,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8665,11 +8662,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8687,11 +8684,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8709,11 +8706,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8731,11 +8728,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8753,11 +8750,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8775,11 +8772,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8797,11 +8794,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8819,11 +8816,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8841,11 +8838,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8863,11 +8860,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8885,11 +8882,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8907,11 +8904,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8929,11 +8926,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8951,11 +8948,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8973,11 +8970,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8995,11 +8992,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -9017,11 +9014,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9039,11 +9036,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9061,11 +9058,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9083,11 +9080,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9105,11 +9102,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I325:I388" si="12">IF(SUM(B325:F325,H325)=0,"",SUM(B325:F325,H325))</f>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J325:J388" si="13">IF(I325="","",1440-I325)</f>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9127,11 +9124,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9149,11 +9146,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9171,11 +9168,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9193,11 +9190,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9215,11 +9212,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -9237,11 +9234,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -9259,11 +9256,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9281,11 +9278,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9303,11 +9300,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9325,11 +9322,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9347,11 +9344,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9369,11 +9366,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9391,11 +9388,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9413,11 +9410,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9435,11 +9432,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9457,11 +9454,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9479,11 +9476,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9501,11 +9498,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9523,11 +9520,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9545,11 +9542,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9567,11 +9564,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9589,11 +9586,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9611,11 +9608,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9633,11 +9630,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9655,11 +9652,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9677,11 +9674,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9699,11 +9696,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9721,11 +9718,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9743,11 +9740,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9765,11 +9762,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9787,11 +9784,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9809,11 +9806,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9831,11 +9828,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9853,11 +9850,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9875,11 +9872,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9897,11 +9894,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9919,11 +9916,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9941,11 +9938,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9963,11 +9960,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9985,11 +9982,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -10007,11 +10004,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -10029,11 +10026,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10051,11 +10048,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10073,11 +10070,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10095,11 +10092,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -10117,11 +10114,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -10139,11 +10136,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -10161,11 +10158,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -10183,11 +10180,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -10205,11 +10202,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10227,11 +10224,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10249,11 +10246,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10271,11 +10268,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10293,11 +10290,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10315,11 +10312,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10337,11 +10334,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10359,11 +10356,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10381,11 +10378,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10403,11 +10400,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10425,11 +10422,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10447,11 +10444,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10469,11 +10466,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10491,11 +10488,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10513,11 +10510,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I389:I399" si="14">IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J389:J399" si="15">IF(I389="","",1440-I389)</f>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10535,11 +10532,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10557,11 +10554,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10579,11 +10576,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10601,11 +10598,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10623,11 +10620,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10645,11 +10642,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10667,11 +10664,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10689,11 +10686,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10711,11 +10708,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10733,11 +10730,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10747,47 +10744,19 @@
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A400" s="13"/>
-      <c r="B400" s="14"/>
-      <c r="C400" s="14"/>
-      <c r="D400" s="14"/>
-      <c r="E400" s="14"/>
-      <c r="F400" s="14"/>
-      <c r="G400" s="14"/>
-      <c r="H400" s="14"/>
-      <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K400" s="16"/>
-      <c r="L400" s="16"/>
-      <c r="M400" s="16"/>
-      <c r="N400" s="17"/>
-    </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A401" s="13"/>
-      <c r="B401" s="14"/>
-      <c r="C401" s="14"/>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-      <c r="F401" s="14"/>
-      <c r="G401" s="14"/>
-      <c r="H401" s="14"/>
-      <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="16"/>
-      <c r="L401" s="16"/>
-      <c r="M401" s="16"/>
-      <c r="N401" s="17"/>
+      <c r="B400" s="13"/>
+      <c r="C400" s="13"/>
+      <c r="D400" s="13"/>
+      <c r="E400" s="13"/>
+      <c r="F400" s="13"/>
+      <c r="G400" s="13"/>
+      <c r="H400" s="13"/>
+      <c r="I400" s="13"/>
+      <c r="J400" s="13"/>
+      <c r="K400" s="13"/>
+      <c r="L400" s="13"/>
+      <c r="M400" s="13"/>
+      <c r="N400" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -10798,21 +10767,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J399">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K399">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L399">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M399">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
